--- a/output/pdf_financials_xlsx/HWX.xlsx
+++ b/output/pdf_financials_xlsx/HWX.xlsx
@@ -855,37 +855,37 @@
         </is>
       </c>
       <c r="B9" s="3" t="n">
-        <v>0</v>
+        <v>5.001</v>
       </c>
       <c r="C9" s="3" t="n">
-        <v>0</v>
+        <v>1.979</v>
       </c>
       <c r="D9" s="3" t="n">
-        <v>0</v>
+        <v>0.606</v>
       </c>
       <c r="E9" s="3" t="n">
-        <v>0</v>
+        <v>0.679</v>
       </c>
       <c r="F9" s="3" t="n">
-        <v>0</v>
+        <v>0.058</v>
       </c>
       <c r="G9" s="3" t="n">
-        <v>0</v>
+        <v>0.74</v>
       </c>
       <c r="H9" s="3" t="n">
-        <v>0</v>
+        <v>1.434</v>
       </c>
       <c r="I9" s="3" t="n">
-        <v>0</v>
+        <v>0.371</v>
       </c>
       <c r="J9" s="3" t="n">
-        <v>0</v>
+        <v>0.276</v>
       </c>
       <c r="K9" s="3" t="n">
-        <v>0</v>
+        <v>0.394</v>
       </c>
       <c r="L9" s="3" t="n">
-        <v>0</v>
+        <v>0.506</v>
       </c>
       <c r="M9" s="3" t="n">
         <v>0</v>
@@ -2037,34 +2037,34 @@
         <v>0</v>
       </c>
       <c r="D28" s="3" t="n">
-        <v>0</v>
+        <v>18.749</v>
       </c>
       <c r="E28" s="3" t="n">
-        <v>0</v>
+        <v>16.982</v>
       </c>
       <c r="F28" s="3" t="n">
-        <v>0</v>
+        <v>11.254</v>
       </c>
       <c r="G28" s="3" t="n">
-        <v>0</v>
+        <v>8.631</v>
       </c>
       <c r="H28" s="3" t="n">
-        <v>0</v>
+        <v>9.029999999999999</v>
       </c>
       <c r="I28" s="3" t="n">
-        <v>0</v>
+        <v>5.178</v>
       </c>
       <c r="J28" s="3" t="n">
-        <v>0</v>
+        <v>5.145</v>
       </c>
       <c r="K28" s="3" t="n">
-        <v>0</v>
+        <v>2.649</v>
       </c>
       <c r="L28" s="3" t="n">
-        <v>0</v>
+        <v>4.871</v>
       </c>
       <c r="M28" s="3" t="n">
-        <v>0</v>
+        <v>4.762</v>
       </c>
       <c r="N28" s="3" t="n">
         <v>44.388</v>
@@ -2095,34 +2095,34 @@
         <v>-0.778</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-8.384</v>
+        <v>10.365</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>-106.959</v>
+        <v>-89.977</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>-64.991</v>
+        <v>-53.737</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>29.995</v>
+        <v>38.626</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>-26.301</v>
+        <v>-17.271</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>-21.225</v>
+        <v>-16.047</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>-17.835</v>
+        <v>-12.69</v>
       </c>
       <c r="K29" s="3" t="n">
-        <v>15.309</v>
+        <v>17.958</v>
       </c>
       <c r="L29" s="3" t="n">
-        <v>-1.923</v>
+        <v>2.948</v>
       </c>
       <c r="M29" s="3" t="n">
-        <v>3.568</v>
+        <v>8.33</v>
       </c>
       <c r="N29" s="3" t="n">
         <v>95.28</v>
@@ -2153,34 +2153,34 @@
         <v>-1.588111616893588</v>
       </c>
       <c r="D30" s="3" t="n">
-        <v>-28.36457135124163</v>
+        <v>35.06664862304621</v>
       </c>
       <c r="E30" s="3" t="n">
-        <v>-445.7925228191556</v>
+        <v>-375.0135456174718</v>
       </c>
       <c r="F30" s="3" t="n">
-        <v>-439.276782696857</v>
+        <v>-363.2105441027375</v>
       </c>
       <c r="G30" s="3" t="n">
-        <v>138.7436976733429</v>
+        <v>178.6669133632453</v>
       </c>
       <c r="H30" s="3" t="n">
-        <v>-113.107986066314</v>
+        <v>-74.27428718874984</v>
       </c>
       <c r="I30" s="3" t="n">
-        <v>-133.692365835223</v>
+        <v>-101.0770975056689</v>
       </c>
       <c r="J30" s="3" t="n">
-        <v>-131.7110996233661</v>
+        <v>-93.71538291115871</v>
       </c>
       <c r="K30" s="3" t="n">
-        <v>199.4917904612979</v>
+        <v>234.0109460516028</v>
       </c>
       <c r="L30" s="3" t="n">
-        <v>-11.34915014164306</v>
+        <v>17.39848914069877</v>
       </c>
       <c r="M30" s="3" t="n">
-        <v>38.22993678345655</v>
+        <v>89.25318761384335</v>
       </c>
       <c r="N30" s="3" t="n">
         <v>49.90049230124647</v>
@@ -6207,34 +6207,34 @@
         <v>0</v>
       </c>
       <c r="D100" s="3" t="n">
-        <v>0</v>
+        <v>18.749</v>
       </c>
       <c r="E100" s="3" t="n">
-        <v>0</v>
+        <v>16.982</v>
       </c>
       <c r="F100" s="3" t="n">
-        <v>0</v>
+        <v>11.254</v>
       </c>
       <c r="G100" s="3" t="n">
-        <v>0</v>
+        <v>8.631</v>
       </c>
       <c r="H100" s="3" t="n">
-        <v>0</v>
+        <v>9.029999999999999</v>
       </c>
       <c r="I100" s="3" t="n">
-        <v>0</v>
+        <v>5.178</v>
       </c>
       <c r="J100" s="3" t="n">
-        <v>0</v>
+        <v>5.145</v>
       </c>
       <c r="K100" s="3" t="n">
-        <v>0</v>
+        <v>2.649</v>
       </c>
       <c r="L100" s="3" t="n">
-        <v>0</v>
+        <v>4.871</v>
       </c>
       <c r="M100" s="3" t="n">
-        <v>0</v>
+        <v>4.762</v>
       </c>
       <c r="N100" s="3" t="n">
         <v>0</v>
@@ -7251,31 +7251,31 @@
         <v>0</v>
       </c>
       <c r="D118" s="3" t="n">
-        <v>0</v>
+        <v>-9.317</v>
       </c>
       <c r="E118" s="3" t="n">
-        <v>0</v>
+        <v>-7.786</v>
       </c>
       <c r="F118" s="3" t="n">
-        <v>0</v>
+        <v>-3.562</v>
       </c>
       <c r="G118" s="3" t="n">
-        <v>0</v>
+        <v>-2.064</v>
       </c>
       <c r="H118" s="3" t="n">
-        <v>0</v>
+        <v>-4.255</v>
       </c>
       <c r="I118" s="3" t="n">
-        <v>0</v>
+        <v>-0.538</v>
       </c>
       <c r="J118" s="3" t="n">
-        <v>0</v>
+        <v>-0.357</v>
       </c>
       <c r="K118" s="3" t="n">
-        <v>0</v>
+        <v>-2.928</v>
       </c>
       <c r="L118" s="3" t="n">
-        <v>0</v>
+        <v>-1.248</v>
       </c>
       <c r="M118" s="3" t="n">
         <v>0</v>
@@ -7293,7 +7293,7 @@
         <v>0</v>
       </c>
       <c r="R118" s="3" t="n">
-        <v>0</v>
+        <v>8.256</v>
       </c>
     </row>
     <row r="119">
@@ -8928,7 +8928,11 @@
           <t>Prepaids and deposits</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr"/>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>PrepaidAssets</t>
+        </is>
+      </c>
       <c r="E7" t="inlineStr">
         <is>
           <t>-</t>
@@ -29955,7 +29959,11 @@
           <t>Exploration and evaluation expense</t>
         </is>
       </c>
-      <c r="D220" t="inlineStr"/>
+      <c r="D220" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E220" t="inlineStr">
         <is>
           <t>-</t>
@@ -38495,7 +38503,7 @@
       </c>
       <c r="D306" t="inlineStr">
         <is>
-          <t>Amortization</t>
+          <t>DepreciationAndAmortization</t>
         </is>
       </c>
       <c r="E306" t="inlineStr">
@@ -41701,7 +41709,7 @@
       </c>
       <c r="D338" t="inlineStr">
         <is>
-          <t>Amortization</t>
+          <t>DepreciationAndAmortization</t>
         </is>
       </c>
       <c r="E338" t="inlineStr">
@@ -42799,7 +42807,11 @@
           <t>Exploration and evaluation expenditures</t>
         </is>
       </c>
-      <c r="D350" t="inlineStr"/>
+      <c r="D350" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E350" t="inlineStr">
         <is>
           <t>-</t>
@@ -60240,7 +60252,7 @@
       </c>
       <c r="D529" t="inlineStr">
         <is>
-          <t>Amortization</t>
+          <t>DepreciationAndAmortization</t>
         </is>
       </c>
       <c r="E529" t="inlineStr">
@@ -61135,7 +61147,11 @@
           <t>Royalty expense</t>
         </is>
       </c>
-      <c r="D538" t="inlineStr"/>
+      <c r="D538" t="inlineStr">
+        <is>
+          <t>OtherOperatingExpenses</t>
+        </is>
+      </c>
       <c r="E538" t="inlineStr">
         <is>
           <t>-</t>
@@ -61147,13 +61163,13 @@
         </is>
       </c>
       <c r="G538" s="5" t="n">
-        <v>-0.606</v>
+        <v>0.606</v>
       </c>
       <c r="H538" s="5" t="n">
-        <v>-0.679</v>
+        <v>0.679</v>
       </c>
       <c r="I538" s="5" t="n">
-        <v>-0.058</v>
+        <v>0.058</v>
       </c>
       <c r="J538" t="inlineStr">
         <is>
@@ -61161,19 +61177,19 @@
         </is>
       </c>
       <c r="K538" s="5" t="n">
-        <v>-1.434</v>
+        <v>1.434</v>
       </c>
       <c r="L538" s="5" t="n">
-        <v>-0.371</v>
+        <v>0.371</v>
       </c>
       <c r="M538" s="5" t="n">
-        <v>-0.276</v>
+        <v>0.276</v>
       </c>
       <c r="N538" s="5" t="n">
-        <v>-0.394</v>
+        <v>0.394</v>
       </c>
       <c r="O538" s="5" t="n">
-        <v>-0.506</v>
+        <v>0.506</v>
       </c>
       <c r="P538" t="inlineStr">
         <is>
@@ -61406,7 +61422,7 @@
       </c>
       <c r="D541" t="inlineStr">
         <is>
-          <t>Amortization</t>
+          <t>DepreciationAndAmortization</t>
         </is>
       </c>
       <c r="E541" t="inlineStr">
@@ -66373,7 +66389,11 @@
           <t>Royalty expense</t>
         </is>
       </c>
-      <c r="D592" t="inlineStr"/>
+      <c r="D592" t="inlineStr">
+        <is>
+          <t>OtherOperatingExpenses</t>
+        </is>
+      </c>
       <c r="E592" t="inlineStr">
         <is>
           <t>-</t>
@@ -66395,13 +66415,13 @@
         </is>
       </c>
       <c r="I592" s="5" t="n">
-        <v>-0.058</v>
+        <v>0.058</v>
       </c>
       <c r="J592" s="5" t="n">
-        <v>-0.74</v>
+        <v>0.74</v>
       </c>
       <c r="K592" s="5" t="n">
-        <v>-1.434</v>
+        <v>1.434</v>
       </c>
       <c r="L592" t="inlineStr">
         <is>
@@ -69377,15 +69397,19 @@
           <t>Royalty expense</t>
         </is>
       </c>
-      <c r="D622" t="inlineStr"/>
+      <c r="D622" t="inlineStr">
+        <is>
+          <t>OtherOperatingExpenses</t>
+        </is>
+      </c>
       <c r="E622" s="5" t="n">
-        <v>-5.001</v>
+        <v>5.001</v>
       </c>
       <c r="F622" s="5" t="n">
-        <v>-1.979</v>
+        <v>1.979</v>
       </c>
       <c r="G622" s="5" t="n">
-        <v>-0.606</v>
+        <v>0.606</v>
       </c>
       <c r="H622" t="inlineStr">
         <is>

--- a/output/pdf_financials_xlsx/HWX.xlsx
+++ b/output/pdf_financials_xlsx/HWX.xlsx
@@ -1065,13 +1065,13 @@
         <v>0</v>
       </c>
       <c r="N12" s="3" t="n">
-        <v>0</v>
+        <v>0.663</v>
       </c>
       <c r="O12" s="3" t="n">
-        <v>0</v>
+        <v>3.844</v>
       </c>
       <c r="P12" s="3" t="n">
-        <v>0</v>
+        <v>6.519</v>
       </c>
       <c r="Q12" s="3" t="n">
         <v>0</v>
@@ -2009,13 +2009,13 @@
         <v>3.568</v>
       </c>
       <c r="N27" s="3" t="n">
-        <v>50.892</v>
+        <v>50.229</v>
       </c>
       <c r="O27" s="3" t="n">
-        <v>211.675</v>
+        <v>207.831</v>
       </c>
       <c r="P27" s="3" t="n">
-        <v>202.974</v>
+        <v>196.455</v>
       </c>
       <c r="Q27" s="3" t="n">
         <v>245.489</v>
@@ -2125,13 +2125,13 @@
         <v>8.33</v>
       </c>
       <c r="N29" s="3" t="n">
-        <v>95.28</v>
+        <v>94.617</v>
       </c>
       <c r="O29" s="3" t="n">
-        <v>291.082</v>
+        <v>287.238</v>
       </c>
       <c r="P29" s="3" t="n">
-        <v>323.171</v>
+        <v>316.652</v>
       </c>
       <c r="Q29" s="3" t="n">
         <v>370.372</v>
@@ -2183,13 +2183,13 @@
         <v>89.25318761384335</v>
       </c>
       <c r="N30" s="3" t="n">
-        <v>49.90049230124647</v>
+        <v>49.55326280506965</v>
       </c>
       <c r="O30" s="3" t="n">
-        <v>63.50247284452385</v>
+        <v>62.66386549122015</v>
       </c>
       <c r="P30" s="3" t="n">
-        <v>63.21390987297401</v>
+        <v>61.93875994163142</v>
       </c>
       <c r="Q30" s="3" t="n">
         <v>59.75631005930907</v>
@@ -55985,7 +55985,7 @@
       </c>
       <c r="D486" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E486" t="inlineStr">

--- a/output/pdf_financials_xlsx/HWX.xlsx
+++ b/output/pdf_financials_xlsx/HWX.xlsx
@@ -4293,28 +4293,28 @@
         <v>0</v>
       </c>
       <c r="E67" s="3" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="F67" s="3" t="n">
-        <v>0</v>
+        <v>0.716</v>
       </c>
       <c r="G67" s="3" t="n">
-        <v>0</v>
+        <v>1.254</v>
       </c>
       <c r="H67" s="3" t="n">
-        <v>0</v>
+        <v>1.659</v>
       </c>
       <c r="I67" s="3" t="n">
         <v>0</v>
       </c>
       <c r="J67" s="3" t="n">
-        <v>0</v>
+        <v>0.437</v>
       </c>
       <c r="K67" s="3" t="n">
-        <v>0</v>
+        <v>0.384</v>
       </c>
       <c r="L67" s="3" t="n">
-        <v>0</v>
+        <v>0.459</v>
       </c>
       <c r="M67" s="3" t="n">
         <v>0</v>
@@ -6176,7 +6176,7 @@
         <v>-0.314</v>
       </c>
       <c r="M99" s="3" t="n">
-        <v>-0.314</v>
+        <v>2.815</v>
       </c>
       <c r="N99" s="3" t="n">
         <v>45.828</v>
@@ -6579,25 +6579,25 @@
         <v>0</v>
       </c>
       <c r="L106" s="3" t="n">
-        <v>0</v>
+        <v>-0.117</v>
       </c>
       <c r="M106" s="3" t="n">
-        <v>0</v>
+        <v>0.655</v>
       </c>
       <c r="N106" s="3" t="n">
-        <v>0</v>
+        <v>-6.26</v>
       </c>
       <c r="O106" s="3" t="n">
-        <v>0</v>
+        <v>-10.195</v>
       </c>
       <c r="P106" s="3" t="n">
-        <v>0</v>
+        <v>7.05</v>
       </c>
       <c r="Q106" s="3" t="n">
-        <v>0</v>
+        <v>-12.096</v>
       </c>
       <c r="R106" s="3" t="n">
-        <v>0</v>
+        <v>-13.205</v>
       </c>
     </row>
     <row r="107">
@@ -6622,19 +6622,19 @@
         <v>1.554</v>
       </c>
       <c r="G107" s="3" t="n">
-        <v>0</v>
+        <v>0.149</v>
       </c>
       <c r="H107" s="3" t="n">
-        <v>0</v>
+        <v>0.458</v>
       </c>
       <c r="I107" s="3" t="n">
-        <v>0</v>
+        <v>0.427</v>
       </c>
       <c r="J107" s="3" t="n">
-        <v>0</v>
+        <v>0.354</v>
       </c>
       <c r="K107" s="3" t="n">
-        <v>0</v>
+        <v>0.24</v>
       </c>
       <c r="L107" s="3" t="n">
         <v>0.847</v>
@@ -6811,10 +6811,10 @@
         <v>0</v>
       </c>
       <c r="L110" s="3" t="n">
-        <v>0</v>
+        <v>0.267</v>
       </c>
       <c r="M110" s="3" t="n">
-        <v>0</v>
+        <v>0.219</v>
       </c>
       <c r="N110" s="3" t="n">
         <v>0</v>
@@ -30553,7 +30553,11 @@
           <t>Change in non-cash operating working capital (note 15)</t>
         </is>
       </c>
-      <c r="D226" t="inlineStr"/>
+      <c r="D226" t="inlineStr">
+        <is>
+          <t>ChangeInWorkingCapital</t>
+        </is>
+      </c>
       <c r="E226" t="inlineStr">
         <is>
           <t>-</t>
@@ -38402,7 +38406,11 @@
           <t>Net income (loss)</t>
         </is>
       </c>
-      <c r="D305" t="inlineStr"/>
+      <c r="D305" t="inlineStr">
+        <is>
+          <t>NetIncomeFromContinuingOperations</t>
+        </is>
+      </c>
       <c r="E305" t="inlineStr">
         <is>
           <t>-</t>
@@ -38901,7 +38909,11 @@
           <t>Deferred income tax expense (recovery)</t>
         </is>
       </c>
-      <c r="D310" t="inlineStr"/>
+      <c r="D310" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E310" t="inlineStr">
         <is>
           <t>-</t>
@@ -39000,7 +39012,11 @@
           <t>Accretion</t>
         </is>
       </c>
-      <c r="D311" t="inlineStr"/>
+      <c r="D311" t="inlineStr">
+        <is>
+          <t>OtherNonCashItems</t>
+        </is>
+      </c>
       <c r="E311" t="inlineStr">
         <is>
           <t>-</t>
@@ -41519,7 +41535,11 @@
           <t>Net income (loss) $</t>
         </is>
       </c>
-      <c r="D336" t="inlineStr"/>
+      <c r="D336" t="inlineStr">
+        <is>
+          <t>NetIncomeFromContinuingOperations</t>
+        </is>
+      </c>
       <c r="E336" t="inlineStr">
         <is>
           <t>-</t>
@@ -41796,7 +41816,11 @@
           <t>Share-based compensation expense</t>
         </is>
       </c>
-      <c r="D339" t="inlineStr"/>
+      <c r="D339" t="inlineStr">
+        <is>
+          <t>StockBasedCompensation</t>
+        </is>
+      </c>
       <c r="E339" t="inlineStr">
         <is>
           <t>-</t>
@@ -41885,7 +41909,11 @@
           <t>Deferred income tax recovery</t>
         </is>
       </c>
-      <c r="D340" t="inlineStr"/>
+      <c r="D340" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E340" t="inlineStr">
         <is>
           <t>-</t>
@@ -43893,7 +43921,11 @@
           <t>Deferred income tax expense (recovery)</t>
         </is>
       </c>
-      <c r="D362" t="inlineStr"/>
+      <c r="D362" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E362" t="inlineStr">
         <is>
           <t>-</t>
@@ -44657,7 +44689,11 @@
           <t>Deferred income tax expense</t>
         </is>
       </c>
-      <c r="D370" t="inlineStr"/>
+      <c r="D370" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E370" t="inlineStr">
         <is>
           <t>-</t>
@@ -47306,7 +47342,11 @@
           <t>Future income tax recovery</t>
         </is>
       </c>
-      <c r="D397" t="inlineStr"/>
+      <c r="D397" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E397" t="inlineStr">
         <is>
           <t>-</t>
@@ -62647,7 +62687,11 @@
           <t>Deferred income tax recovery (note 9)</t>
         </is>
       </c>
-      <c r="D554" t="inlineStr"/>
+      <c r="D554" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E554" t="inlineStr">
         <is>
           <t>-</t>
@@ -68385,7 +68429,11 @@
           <t>Deferred income tax recovery (note 8)</t>
         </is>
       </c>
-      <c r="D612" t="inlineStr"/>
+      <c r="D612" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E612" t="inlineStr">
         <is>
           <t>-</t>
@@ -69094,7 +69142,11 @@
           <t>Deferred income tax recovery (note 7)</t>
         </is>
       </c>
-      <c r="D619" t="inlineStr"/>
+      <c r="D619" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E619" t="inlineStr">
         <is>
           <t>-</t>
@@ -70793,7 +70845,11 @@
           <t>Future income tax recovery (note 5)</t>
         </is>
       </c>
-      <c r="D636" t="inlineStr"/>
+      <c r="D636" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E636" t="inlineStr">
         <is>
           <t>-</t>
